--- a/docs/CodeSystem-mars-landing-sites-cs.xlsx
+++ b/docs/CodeSystem-mars-landing-sites-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-mars-landing-sites-cs.xlsx
+++ b/docs/CodeSystem-mars-landing-sites-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-mars-landing-sites-cs.xlsx
+++ b/docs/CodeSystem-mars-landing-sites-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-mars-landing-sites-cs.xlsx
+++ b/docs/CodeSystem-mars-landing-sites-cs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-mars-landing-sites-cs.xlsx
+++ b/docs/CodeSystem-mars-landing-sites-cs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -25,13 +25,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/mars-landing-sites-cs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/mars-landing-sites-cs</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -55,13 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,8 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Candidate landing sites for human Mars missions with are
-ographic coordinates and site characteristics</t>
+    <t>Candidate landing sites for human Mars missions with areographic coordinates and site characteristics</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -95,12 +94,12 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Value Set (all codes)</t>
   </si>
   <si>
@@ -140,9 +139,6 @@
     <t>latitude</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/mars-landing-sites-cs#latitude</t>
-  </si>
-  <si>
     <t>Areographic latitude (degrees, -90 to +90)</t>
   </si>
   <si>
@@ -152,16 +148,10 @@
     <t>longitude</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/mars-landing-sites-cs#longitude</t>
-  </si>
-  <si>
     <t>Areographic longitude (degrees, 0 to 360)</t>
   </si>
   <si>
     <t>feature</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/aerospace/CodeSystem/mars-landing-sites-cs#feature</t>
   </si>
   <si>
     <t>Primary topographic feature</t>
@@ -480,14 +470,16 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -564,42 +556,36 @@
       <c r="A2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2"/>
+      <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -614,100 +600,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
